--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -7040,7 +7040,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -7040,7 +7040,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251019_201404.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
